--- a/data_nof1_caffeine.xlsx
+++ b/data_nof1_caffeine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/70ed252595cc6131/Anexos/stats/teixeira/nof1_caffeine/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="11_EE61FDCE8F79A8D366075C52F3CAC271BA93E126" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B829C9C7-2DE4-4714-A1F9-431E884D49CE}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="11_EE61FDCE8F79A8D366075C52F3CAC271BA93E126" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D0540A7-C822-4EFC-AC07-0AC0EBF2BCAA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,15 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="29">
   <si>
     <t>Cycle</t>
   </si>
   <si>
     <t>Period</t>
-  </si>
-  <si>
-    <t>Treatment</t>
   </si>
   <si>
     <t>date</t>
@@ -44,12 +41,6 @@
   </si>
   <si>
     <t>x4</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
   </si>
   <si>
     <t>LKI BRONA</t>
@@ -104,6 +95,18 @@
   </si>
   <si>
     <t>order_period_obs</t>
+  </si>
+  <si>
+    <t>Decaf</t>
+  </si>
+  <si>
+    <t>Caf</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>Treatment</t>
   </si>
 </sst>
 </file>
@@ -176,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -194,11 +197,15 @@
     <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
     <dxf>
       <font>
         <strike val="0"/>
@@ -310,6 +317,25 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -469,15 +495,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C75DA212-2CF7-4519-8F74-D63F88BF5D2F}" name="Tabela1" displayName="Tabela1" ref="A1:O53" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
-  <autoFilter ref="A1:O53" xr:uid="{C75DA212-2CF7-4519-8F74-D63F88BF5D2F}"/>
-  <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{486990D1-499E-44FA-90FF-7E10DBADF12E}" name="Cycle" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{7A6A90A2-BF09-43D7-A62E-0C667FC819E2}" name="Period" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{900F9932-82D3-4F15-A98F-DC7BFEE071B4}" name="Treatment" dataDxfId="12"/>
-    <tableColumn id="14" xr3:uid="{29F29B01-4580-4DEF-83F9-6645E434A686}" name="order_cycle_obs" dataDxfId="11"/>
-    <tableColumn id="15" xr3:uid="{CDF8AB43-F934-4952-960E-3C1AF4A7D112}" name="order_period_obs" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{6181479D-B7ED-4138-BBEF-40DCFF695970}" name="date" dataDxfId="9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C75DA212-2CF7-4519-8F74-D63F88BF5D2F}" name="Tabela1" displayName="Tabela1" ref="A1:P53" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+  <autoFilter ref="A1:P53" xr:uid="{C75DA212-2CF7-4519-8F74-D63F88BF5D2F}"/>
+  <tableColumns count="16">
+    <tableColumn id="1" xr3:uid="{486990D1-499E-44FA-90FF-7E10DBADF12E}" name="Cycle" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{7A6A90A2-BF09-43D7-A62E-0C667FC819E2}" name="Period" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{900F9932-82D3-4F15-A98F-DC7BFEE071B4}" name="Treatment" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{29F29B01-4580-4DEF-83F9-6645E434A686}" name="order_cycle_obs" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{CDF8AB43-F934-4952-960E-3C1AF4A7D112}" name="order_period_obs" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{6181479D-B7ED-4138-BBEF-40DCFF695970}" name="date" dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{D42D5DD7-72C9-446B-BD7F-2D428040CD60}" name="time" dataDxfId="9"/>
     <tableColumn id="12" xr3:uid="{04BC6DC8-441E-49B7-9966-E5ADBF226BF8}" name="day_cat" dataDxfId="8"/>
     <tableColumn id="5" xr3:uid="{8434B715-34E8-4A7E-8631-85B36E0EB923}" name="sleep_cont" dataDxfId="7"/>
     <tableColumn id="6" xr3:uid="{621161EA-36BF-4EA8-AFFB-BB9A06283C49}" name="sleep_ord" dataDxfId="6"/>
@@ -816,25 +843,26 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:P53"/>
   <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="7" customWidth="1"/>
     <col min="2" max="2" width="5.5703125" style="7" customWidth="1"/>
     <col min="3" max="5" width="7.140625" style="7" customWidth="1"/>
     <col min="6" max="6" width="10" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" style="10" customWidth="1"/>
-    <col min="8" max="8" width="8.7109375" style="7" customWidth="1"/>
-    <col min="9" max="9" width="8" style="7" customWidth="1"/>
-    <col min="10" max="10" width="8.42578125" style="7" customWidth="1"/>
-    <col min="11" max="11" width="5.7109375" style="7" customWidth="1"/>
-    <col min="12" max="12" width="6.7109375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="9" style="7" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" style="7" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="7"/>
+    <col min="7" max="7" width="10" style="12" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" style="10" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" style="7" customWidth="1"/>
+    <col min="10" max="10" width="8" style="7" customWidth="1"/>
+    <col min="11" max="11" width="8.42578125" style="7" customWidth="1"/>
+    <col min="12" max="12" width="5.7109375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="6.7109375" style="7" customWidth="1"/>
+    <col min="14" max="14" width="9" style="7" customWidth="1"/>
+    <col min="15" max="15" width="8.28515625" style="7" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -842,54 +870,57 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>8</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
@@ -901,32 +932,35 @@
         <v>46129</v>
       </c>
       <c r="G2" s="6">
+        <v>1</v>
+      </c>
+      <c r="H2" s="6">
         <v>6</v>
       </c>
-      <c r="H2" s="4">
+      <c r="I2" s="4">
         <v>30</v>
       </c>
-      <c r="I2" s="4">
-        <v>3</v>
-      </c>
       <c r="J2" s="4">
+        <v>3</v>
+      </c>
+      <c r="K2" s="4">
         <v>119</v>
       </c>
-      <c r="K2" s="4">
+      <c r="L2" s="4">
         <v>59</v>
       </c>
-      <c r="L2" s="4">
+      <c r="M2" s="4">
         <v>75</v>
       </c>
-      <c r="M2" s="4">
+      <c r="N2" s="4">
         <v>90</v>
       </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O2" s="4"/>
+      <c r="P2" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -934,7 +968,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D3" s="4">
         <v>2</v>
@@ -946,30 +980,33 @@
         <v>46130</v>
       </c>
       <c r="G3" s="6">
+        <v>2</v>
+      </c>
+      <c r="H3" s="6">
         <v>7</v>
       </c>
-      <c r="H3" s="4">
+      <c r="I3" s="4">
         <v>34</v>
       </c>
-      <c r="I3" s="4">
-        <v>3</v>
-      </c>
       <c r="J3" s="4">
+        <v>3</v>
+      </c>
+      <c r="K3" s="4">
         <v>105</v>
       </c>
-      <c r="K3" s="4">
+      <c r="L3" s="4">
         <v>74</v>
       </c>
-      <c r="L3" s="4">
+      <c r="M3" s="4">
         <v>63</v>
       </c>
-      <c r="M3" s="4">
+      <c r="N3" s="4">
         <v>91</v>
       </c>
-      <c r="N3" s="4"/>
       <c r="O3" s="4"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P3" s="4"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -977,7 +1014,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D4" s="4">
         <v>3</v>
@@ -989,30 +1026,33 @@
         <v>46131</v>
       </c>
       <c r="G4" s="6">
+        <v>3</v>
+      </c>
+      <c r="H4" s="6">
         <v>8</v>
       </c>
-      <c r="H4" s="4">
+      <c r="I4" s="4">
         <v>27</v>
       </c>
-      <c r="I4" s="4">
-        <v>3</v>
-      </c>
       <c r="J4" s="4">
+        <v>3</v>
+      </c>
+      <c r="K4" s="4">
         <v>111</v>
       </c>
-      <c r="K4" s="4">
+      <c r="L4" s="4">
         <v>80</v>
       </c>
-      <c r="L4" s="4">
+      <c r="M4" s="4">
         <v>72</v>
       </c>
-      <c r="M4" s="4">
+      <c r="N4" s="4">
         <v>85</v>
       </c>
-      <c r="N4" s="4"/>
       <c r="O4" s="4"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P4" s="4"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -1020,7 +1060,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D5" s="4">
         <v>4</v>
@@ -1032,10 +1072,13 @@
         <v>46132</v>
       </c>
       <c r="G5" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="H5" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>2</v>
       </c>
@@ -1043,7 +1086,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D6" s="4">
         <v>1</v>
@@ -1055,28 +1098,31 @@
         <v>46133</v>
       </c>
       <c r="G6" s="6">
-        <v>3</v>
-      </c>
-      <c r="H6" s="7">
+        <v>5</v>
+      </c>
+      <c r="H6" s="6">
+        <v>3</v>
+      </c>
+      <c r="I6" s="7">
         <v>31</v>
       </c>
-      <c r="I6" s="7">
-        <v>3</v>
-      </c>
       <c r="J6" s="7">
+        <v>3</v>
+      </c>
+      <c r="K6" s="7">
         <v>114</v>
       </c>
-      <c r="K6" s="7">
+      <c r="L6" s="7">
         <v>81</v>
       </c>
-      <c r="L6" s="7">
+      <c r="M6" s="7">
         <v>52</v>
       </c>
-      <c r="M6" s="7">
+      <c r="N6" s="7">
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>2</v>
       </c>
@@ -1084,7 +1130,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D7" s="4">
         <v>2</v>
@@ -1096,31 +1142,34 @@
         <v>46134</v>
       </c>
       <c r="G7" s="6">
-        <v>4</v>
-      </c>
-      <c r="H7" s="7">
+        <v>6</v>
+      </c>
+      <c r="H7" s="6">
+        <v>4</v>
+      </c>
+      <c r="I7" s="7">
         <v>33</v>
       </c>
-      <c r="I7" s="7">
-        <v>3</v>
-      </c>
       <c r="J7" s="7">
+        <v>3</v>
+      </c>
+      <c r="K7" s="7">
         <v>113</v>
       </c>
-      <c r="K7" s="7">
+      <c r="L7" s="7">
         <v>79</v>
       </c>
-      <c r="L7" s="7">
+      <c r="M7" s="7">
         <v>65</v>
       </c>
-      <c r="M7" s="7">
+      <c r="N7" s="7">
         <v>76</v>
       </c>
-      <c r="O7" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P7" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>2</v>
       </c>
@@ -1128,7 +1177,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D8" s="4">
         <v>3</v>
@@ -1140,28 +1189,31 @@
         <v>46135</v>
       </c>
       <c r="G8" s="6">
+        <v>7</v>
+      </c>
+      <c r="H8" s="6">
         <v>5</v>
       </c>
-      <c r="H8" s="7">
+      <c r="I8" s="7">
         <v>33</v>
       </c>
-      <c r="I8" s="7">
-        <v>3</v>
-      </c>
       <c r="J8" s="7">
+        <v>3</v>
+      </c>
+      <c r="K8" s="7">
         <v>115</v>
       </c>
-      <c r="K8" s="7">
+      <c r="L8" s="7">
         <v>76</v>
       </c>
-      <c r="L8" s="7">
+      <c r="M8" s="7">
         <v>67</v>
       </c>
-      <c r="M8" s="7">
+      <c r="N8" s="7">
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>2</v>
       </c>
@@ -1169,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D9" s="4">
         <v>4</v>
@@ -1181,28 +1233,31 @@
         <v>46136</v>
       </c>
       <c r="G9" s="6">
+        <v>8</v>
+      </c>
+      <c r="H9" s="6">
         <v>6</v>
       </c>
-      <c r="H9" s="7">
+      <c r="I9" s="7">
         <v>30</v>
       </c>
-      <c r="I9" s="7">
-        <v>3</v>
-      </c>
       <c r="J9" s="7">
+        <v>3</v>
+      </c>
+      <c r="K9" s="7">
         <v>118</v>
       </c>
-      <c r="K9" s="7">
+      <c r="L9" s="7">
         <v>78</v>
       </c>
-      <c r="L9" s="7">
+      <c r="M9" s="7">
         <v>64</v>
       </c>
-      <c r="M9" s="7">
+      <c r="N9" s="7">
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>3</v>
       </c>
@@ -1210,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -1222,31 +1277,34 @@
         <v>46137</v>
       </c>
       <c r="G10" s="6">
+        <v>9</v>
+      </c>
+      <c r="H10" s="6">
         <v>7</v>
       </c>
-      <c r="H10" s="7">
+      <c r="I10" s="7">
         <v>27</v>
       </c>
-      <c r="I10" s="7">
-        <v>3</v>
-      </c>
       <c r="J10" s="7">
+        <v>3</v>
+      </c>
+      <c r="K10" s="7">
         <v>129</v>
       </c>
-      <c r="K10" s="7">
+      <c r="L10" s="7">
         <v>83</v>
       </c>
-      <c r="L10" s="7">
+      <c r="M10" s="7">
         <v>80</v>
       </c>
-      <c r="M10" s="7">
+      <c r="N10" s="7">
         <v>91</v>
       </c>
-      <c r="O10" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P10" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>3</v>
       </c>
@@ -1254,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D11" s="4">
         <v>2</v>
@@ -1266,28 +1324,31 @@
         <v>46138</v>
       </c>
       <c r="G11" s="6">
+        <v>10</v>
+      </c>
+      <c r="H11" s="6">
         <v>8</v>
       </c>
-      <c r="H11" s="7">
+      <c r="I11" s="7">
         <v>24</v>
       </c>
-      <c r="I11" s="7">
-        <v>2</v>
-      </c>
       <c r="J11" s="7">
+        <v>2</v>
+      </c>
+      <c r="K11" s="7">
         <v>106</v>
       </c>
-      <c r="K11" s="7">
+      <c r="L11" s="7">
         <v>76</v>
       </c>
-      <c r="L11" s="7">
+      <c r="M11" s="7">
         <v>68</v>
       </c>
-      <c r="M11" s="7">
+      <c r="N11" s="7">
         <v>93</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>3</v>
       </c>
@@ -1295,7 +1356,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D12" s="4">
         <v>3</v>
@@ -1307,28 +1368,31 @@
         <v>46139</v>
       </c>
       <c r="G12" s="6">
-        <v>2</v>
-      </c>
-      <c r="H12" s="7">
+        <v>11</v>
+      </c>
+      <c r="H12" s="6">
+        <v>2</v>
+      </c>
+      <c r="I12" s="7">
         <v>29</v>
       </c>
-      <c r="I12" s="7">
-        <v>3</v>
-      </c>
       <c r="J12" s="7">
+        <v>3</v>
+      </c>
+      <c r="K12" s="7">
         <v>112</v>
       </c>
-      <c r="K12" s="7">
+      <c r="L12" s="7">
         <v>82</v>
       </c>
-      <c r="L12" s="7">
+      <c r="M12" s="7">
         <v>71</v>
       </c>
-      <c r="M12" s="7">
+      <c r="N12" s="7">
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>3</v>
       </c>
@@ -1336,7 +1400,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D13" s="4">
         <v>4</v>
@@ -1348,28 +1412,31 @@
         <v>46140</v>
       </c>
       <c r="G13" s="6">
-        <v>3</v>
-      </c>
-      <c r="H13" s="7">
+        <v>12</v>
+      </c>
+      <c r="H13" s="6">
+        <v>3</v>
+      </c>
+      <c r="I13" s="7">
         <v>34</v>
       </c>
-      <c r="I13" s="7">
-        <v>3</v>
-      </c>
       <c r="J13" s="7">
+        <v>3</v>
+      </c>
+      <c r="K13" s="7">
         <v>116</v>
       </c>
-      <c r="K13" s="7">
+      <c r="L13" s="7">
         <v>77</v>
       </c>
-      <c r="L13" s="7">
+      <c r="M13" s="7">
         <v>60</v>
       </c>
-      <c r="M13" s="7">
+      <c r="N13" s="7">
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>4</v>
       </c>
@@ -1377,7 +1444,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
@@ -1389,28 +1456,31 @@
         <v>46141</v>
       </c>
       <c r="G14" s="6">
-        <v>4</v>
-      </c>
-      <c r="H14" s="7">
+        <v>13</v>
+      </c>
+      <c r="H14" s="6">
+        <v>4</v>
+      </c>
+      <c r="I14" s="7">
         <v>31</v>
       </c>
-      <c r="I14" s="7">
-        <v>3</v>
-      </c>
       <c r="J14" s="7">
+        <v>3</v>
+      </c>
+      <c r="K14" s="7">
         <v>117</v>
       </c>
-      <c r="K14" s="7">
+      <c r="L14" s="7">
         <v>75</v>
       </c>
-      <c r="L14" s="7">
+      <c r="M14" s="7">
         <v>64</v>
       </c>
-      <c r="M14" s="7">
+      <c r="N14" s="7">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>4</v>
       </c>
@@ -1418,7 +1488,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D15" s="4">
         <v>2</v>
@@ -1430,28 +1500,31 @@
         <v>46142</v>
       </c>
       <c r="G15" s="6">
+        <v>14</v>
+      </c>
+      <c r="H15" s="6">
         <v>5</v>
       </c>
-      <c r="H15" s="7">
+      <c r="I15" s="7">
         <v>38</v>
       </c>
-      <c r="I15" s="7">
-        <v>4</v>
-      </c>
       <c r="J15" s="7">
+        <v>4</v>
+      </c>
+      <c r="K15" s="7">
         <v>114</v>
       </c>
-      <c r="K15" s="7">
+      <c r="L15" s="7">
         <v>74</v>
       </c>
-      <c r="L15" s="7">
+      <c r="M15" s="7">
         <v>59</v>
       </c>
-      <c r="O15" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P15" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>4</v>
       </c>
@@ -1459,7 +1532,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D16" s="4">
         <v>3</v>
@@ -1471,19 +1544,22 @@
         <v>46143</v>
       </c>
       <c r="G16" s="6">
+        <v>15</v>
+      </c>
+      <c r="H16" s="6">
         <v>6</v>
       </c>
-      <c r="H16" s="7">
+      <c r="I16" s="7">
         <v>38</v>
       </c>
-      <c r="I16" s="7">
-        <v>4</v>
-      </c>
-      <c r="M16" s="7">
+      <c r="J16" s="7">
+        <v>4</v>
+      </c>
+      <c r="N16" s="7">
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>4</v>
       </c>
@@ -1491,7 +1567,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D17" s="4">
         <v>4</v>
@@ -1503,28 +1579,31 @@
         <v>46144</v>
       </c>
       <c r="G17" s="6">
+        <v>16</v>
+      </c>
+      <c r="H17" s="6">
         <v>7</v>
       </c>
-      <c r="H17" s="7">
+      <c r="I17" s="7">
         <v>37</v>
       </c>
-      <c r="I17" s="7">
-        <v>4</v>
-      </c>
       <c r="J17" s="7">
+        <v>4</v>
+      </c>
+      <c r="K17" s="7">
         <v>105</v>
       </c>
-      <c r="K17" s="7">
+      <c r="L17" s="7">
         <v>78</v>
       </c>
-      <c r="L17" s="7">
+      <c r="M17" s="7">
         <v>68</v>
       </c>
-      <c r="M17" s="7">
+      <c r="N17" s="7">
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>5</v>
       </c>
@@ -1532,7 +1611,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
@@ -1544,31 +1623,34 @@
         <v>46145</v>
       </c>
       <c r="G18" s="6">
+        <v>17</v>
+      </c>
+      <c r="H18" s="6">
         <v>8</v>
       </c>
-      <c r="H18" s="7">
+      <c r="I18" s="7">
         <v>34</v>
       </c>
-      <c r="I18" s="7">
-        <v>3</v>
-      </c>
       <c r="J18" s="7">
+        <v>3</v>
+      </c>
+      <c r="K18" s="7">
         <v>120</v>
       </c>
-      <c r="K18" s="7">
+      <c r="L18" s="7">
         <v>85</v>
       </c>
-      <c r="L18" s="7">
+      <c r="M18" s="7">
         <v>82</v>
       </c>
-      <c r="M18" s="7">
+      <c r="N18" s="7">
         <v>80</v>
       </c>
-      <c r="O18" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P18" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>5</v>
       </c>
@@ -1576,7 +1658,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D19" s="4">
         <v>2</v>
@@ -1588,28 +1670,31 @@
         <v>46146</v>
       </c>
       <c r="G19" s="6">
-        <v>2</v>
-      </c>
-      <c r="H19" s="7">
+        <v>18</v>
+      </c>
+      <c r="H19" s="6">
+        <v>2</v>
+      </c>
+      <c r="I19" s="7">
         <v>32</v>
       </c>
-      <c r="I19" s="7">
-        <v>3</v>
-      </c>
       <c r="J19" s="7">
+        <v>3</v>
+      </c>
+      <c r="K19" s="7">
         <v>131</v>
       </c>
-      <c r="K19" s="7">
+      <c r="L19" s="7">
         <v>84</v>
       </c>
-      <c r="L19" s="7">
+      <c r="M19" s="7">
         <v>67</v>
       </c>
-      <c r="M19" s="7">
+      <c r="N19" s="7">
         <v>86</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>5</v>
       </c>
@@ -1617,7 +1702,7 @@
         <v>2</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D20" s="4">
         <v>3</v>
@@ -1629,28 +1714,31 @@
         <v>46147</v>
       </c>
       <c r="G20" s="6">
-        <v>3</v>
-      </c>
-      <c r="H20" s="7">
+        <v>19</v>
+      </c>
+      <c r="H20" s="6">
+        <v>3</v>
+      </c>
+      <c r="I20" s="7">
         <v>38</v>
       </c>
-      <c r="I20" s="7">
-        <v>4</v>
-      </c>
       <c r="J20" s="7">
+        <v>4</v>
+      </c>
+      <c r="K20" s="7">
         <v>117</v>
       </c>
-      <c r="K20" s="7">
+      <c r="L20" s="7">
         <v>85</v>
       </c>
-      <c r="L20" s="7">
+      <c r="M20" s="7">
         <v>47</v>
       </c>
-      <c r="M20" s="7">
+      <c r="N20" s="7">
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>5</v>
       </c>
@@ -1658,7 +1746,7 @@
         <v>2</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D21" s="4">
         <v>4</v>
@@ -1670,28 +1758,31 @@
         <v>46148</v>
       </c>
       <c r="G21" s="6">
-        <v>4</v>
-      </c>
-      <c r="H21" s="7">
+        <v>20</v>
+      </c>
+      <c r="H21" s="6">
+        <v>4</v>
+      </c>
+      <c r="I21" s="7">
         <v>34</v>
       </c>
-      <c r="I21" s="7">
-        <v>3</v>
-      </c>
       <c r="J21" s="7">
+        <v>3</v>
+      </c>
+      <c r="K21" s="7">
         <v>119</v>
       </c>
-      <c r="K21" s="7">
+      <c r="L21" s="7">
         <v>84</v>
       </c>
-      <c r="L21" s="7">
+      <c r="M21" s="7">
         <v>60</v>
       </c>
-      <c r="M21" s="7">
+      <c r="N21" s="7">
         <v>78</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>6</v>
       </c>
@@ -1699,7 +1790,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D22" s="4">
         <v>1</v>
@@ -1711,28 +1802,31 @@
         <v>46149</v>
       </c>
       <c r="G22" s="6">
+        <v>21</v>
+      </c>
+      <c r="H22" s="6">
         <v>5</v>
       </c>
-      <c r="H22" s="7">
+      <c r="I22" s="7">
         <v>28</v>
       </c>
-      <c r="I22" s="7">
-        <v>3</v>
-      </c>
       <c r="J22" s="7">
+        <v>3</v>
+      </c>
+      <c r="K22" s="7">
         <v>131</v>
       </c>
-      <c r="K22" s="7">
+      <c r="L22" s="7">
         <v>88</v>
       </c>
-      <c r="L22" s="7">
+      <c r="M22" s="7">
         <v>72</v>
       </c>
-      <c r="M22" s="7">
+      <c r="N22" s="7">
         <v>91</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>6</v>
       </c>
@@ -1740,7 +1834,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D23" s="4">
         <v>2</v>
@@ -1752,28 +1846,31 @@
         <v>46150</v>
       </c>
       <c r="G23" s="6">
+        <v>22</v>
+      </c>
+      <c r="H23" s="6">
         <v>6</v>
       </c>
-      <c r="H23" s="7">
+      <c r="I23" s="7">
         <v>33</v>
       </c>
-      <c r="I23" s="7">
-        <v>3</v>
-      </c>
       <c r="J23" s="7">
+        <v>3</v>
+      </c>
+      <c r="K23" s="7">
         <v>123</v>
       </c>
-      <c r="K23" s="7">
+      <c r="L23" s="7">
         <v>83</v>
       </c>
-      <c r="L23" s="7">
+      <c r="M23" s="7">
         <v>60</v>
       </c>
-      <c r="M23" s="7">
+      <c r="N23" s="7">
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>6</v>
       </c>
@@ -1781,7 +1878,7 @@
         <v>2</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D24" s="4">
         <v>3</v>
@@ -1793,31 +1890,34 @@
         <v>46151</v>
       </c>
       <c r="G24" s="6">
+        <v>23</v>
+      </c>
+      <c r="H24" s="6">
         <v>7</v>
       </c>
-      <c r="H24" s="7">
+      <c r="I24" s="7">
         <v>33</v>
       </c>
-      <c r="I24" s="7">
-        <v>3</v>
-      </c>
       <c r="J24" s="7">
+        <v>3</v>
+      </c>
+      <c r="K24" s="7">
         <v>126</v>
       </c>
-      <c r="K24" s="7">
+      <c r="L24" s="7">
         <v>83</v>
       </c>
-      <c r="L24" s="7">
+      <c r="M24" s="7">
         <v>55</v>
       </c>
-      <c r="M24" s="7">
+      <c r="N24" s="7">
         <v>85</v>
       </c>
-      <c r="O24" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P24" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>6</v>
       </c>
@@ -1825,7 +1925,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D25" s="4">
         <v>4</v>
@@ -1837,28 +1937,31 @@
         <v>46152</v>
       </c>
       <c r="G25" s="6">
+        <v>24</v>
+      </c>
+      <c r="H25" s="6">
         <v>8</v>
       </c>
-      <c r="H25" s="7">
+      <c r="I25" s="7">
         <v>38</v>
       </c>
-      <c r="I25" s="7">
-        <v>4</v>
-      </c>
       <c r="J25" s="7">
+        <v>4</v>
+      </c>
+      <c r="K25" s="7">
         <v>125</v>
       </c>
-      <c r="K25" s="7">
+      <c r="L25" s="7">
         <v>84</v>
       </c>
-      <c r="L25" s="7">
+      <c r="M25" s="7">
         <v>60</v>
       </c>
-      <c r="M25" s="7">
+      <c r="N25" s="7">
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>7</v>
       </c>
@@ -1866,7 +1969,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D26" s="4">
         <v>1</v>
@@ -1878,28 +1981,31 @@
         <v>46153</v>
       </c>
       <c r="G26" s="6">
-        <v>2</v>
-      </c>
-      <c r="H26" s="7">
+        <v>25</v>
+      </c>
+      <c r="H26" s="6">
+        <v>2</v>
+      </c>
+      <c r="I26" s="7">
         <v>30</v>
       </c>
-      <c r="I26" s="7">
-        <v>3</v>
-      </c>
       <c r="J26" s="7">
+        <v>3</v>
+      </c>
+      <c r="K26" s="7">
         <v>134</v>
       </c>
-      <c r="K26" s="7">
+      <c r="L26" s="7">
         <v>91</v>
       </c>
-      <c r="L26" s="7">
+      <c r="M26" s="7">
         <v>69</v>
       </c>
-      <c r="M26" s="7">
+      <c r="N26" s="7">
         <v>95</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>7</v>
       </c>
@@ -1907,7 +2013,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D27" s="4">
         <v>2</v>
@@ -1919,31 +2025,34 @@
         <v>46154</v>
       </c>
       <c r="G27" s="6">
-        <v>3</v>
-      </c>
-      <c r="H27" s="7">
+        <v>26</v>
+      </c>
+      <c r="H27" s="6">
+        <v>3</v>
+      </c>
+      <c r="I27" s="7">
         <v>31</v>
       </c>
-      <c r="I27" s="7">
-        <v>3</v>
-      </c>
       <c r="J27" s="7">
+        <v>3</v>
+      </c>
+      <c r="K27" s="7">
         <v>120</v>
       </c>
-      <c r="K27" s="7">
+      <c r="L27" s="7">
         <v>79</v>
       </c>
-      <c r="L27" s="7">
+      <c r="M27" s="7">
         <v>60</v>
       </c>
-      <c r="M27" s="7">
+      <c r="N27" s="7">
         <v>82</v>
       </c>
-      <c r="O27" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P27" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>7</v>
       </c>
@@ -1951,7 +2060,7 @@
         <v>2</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D28" s="4">
         <v>3</v>
@@ -1963,28 +2072,31 @@
         <v>46155</v>
       </c>
       <c r="G28" s="6">
-        <v>4</v>
-      </c>
-      <c r="H28" s="7">
+        <v>27</v>
+      </c>
+      <c r="H28" s="6">
+        <v>4</v>
+      </c>
+      <c r="I28" s="7">
         <v>34</v>
       </c>
-      <c r="I28" s="7">
-        <v>3</v>
-      </c>
       <c r="J28" s="7">
+        <v>3</v>
+      </c>
+      <c r="K28" s="7">
         <v>112</v>
       </c>
-      <c r="K28" s="7">
+      <c r="L28" s="7">
         <v>80</v>
       </c>
-      <c r="L28" s="7">
+      <c r="M28" s="7">
         <v>68</v>
       </c>
-      <c r="M28" s="7">
+      <c r="N28" s="7">
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>7</v>
       </c>
@@ -1992,7 +2104,7 @@
         <v>2</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D29" s="4">
         <v>4</v>
@@ -2004,28 +2116,31 @@
         <v>46156</v>
       </c>
       <c r="G29" s="6">
+        <v>28</v>
+      </c>
+      <c r="H29" s="6">
         <v>5</v>
       </c>
-      <c r="H29" s="7">
+      <c r="I29" s="7">
         <v>39</v>
       </c>
-      <c r="I29" s="7">
-        <v>4</v>
-      </c>
       <c r="J29" s="7">
+        <v>4</v>
+      </c>
+      <c r="K29" s="7">
         <v>120</v>
       </c>
-      <c r="K29" s="7">
+      <c r="L29" s="7">
         <v>83</v>
       </c>
-      <c r="L29" s="7">
+      <c r="M29" s="7">
         <v>58</v>
       </c>
-      <c r="M29" s="7">
+      <c r="N29" s="7">
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>8</v>
       </c>
@@ -2033,7 +2148,7 @@
         <v>1</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D30" s="4">
         <v>1</v>
@@ -2045,28 +2160,31 @@
         <v>46157</v>
       </c>
       <c r="G30" s="6">
+        <v>29</v>
+      </c>
+      <c r="H30" s="6">
         <v>6</v>
       </c>
-      <c r="H30" s="7">
+      <c r="I30" s="7">
         <v>34</v>
       </c>
-      <c r="I30" s="7">
-        <v>3</v>
-      </c>
       <c r="J30" s="7">
+        <v>3</v>
+      </c>
+      <c r="K30" s="7">
         <v>131</v>
       </c>
-      <c r="K30" s="7">
+      <c r="L30" s="7">
         <v>83</v>
       </c>
-      <c r="L30" s="7">
+      <c r="M30" s="7">
         <v>69</v>
       </c>
-      <c r="M30" s="7">
+      <c r="N30" s="7">
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>8</v>
       </c>
@@ -2074,7 +2192,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D31" s="4">
         <v>2</v>
@@ -2086,28 +2204,31 @@
         <v>46158</v>
       </c>
       <c r="G31" s="6">
+        <v>30</v>
+      </c>
+      <c r="H31" s="6">
         <v>7</v>
       </c>
-      <c r="H31" s="7">
+      <c r="I31" s="7">
         <v>34</v>
       </c>
-      <c r="I31" s="7">
-        <v>3</v>
-      </c>
       <c r="J31" s="7">
+        <v>3</v>
+      </c>
+      <c r="K31" s="7">
         <v>122</v>
       </c>
-      <c r="K31" s="7">
+      <c r="L31" s="7">
         <v>80</v>
       </c>
-      <c r="L31" s="7">
+      <c r="M31" s="7">
         <v>78</v>
       </c>
-      <c r="M31" s="7">
+      <c r="N31" s="7">
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>8</v>
       </c>
@@ -2115,7 +2236,7 @@
         <v>2</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D32" s="4">
         <v>3</v>
@@ -2127,31 +2248,34 @@
         <v>46159</v>
       </c>
       <c r="G32" s="6">
+        <v>31</v>
+      </c>
+      <c r="H32" s="6">
         <v>8</v>
       </c>
-      <c r="H32" s="7">
+      <c r="I32" s="7">
         <v>35</v>
       </c>
-      <c r="I32" s="7">
-        <v>3</v>
-      </c>
       <c r="J32" s="7">
+        <v>3</v>
+      </c>
+      <c r="K32" s="7">
         <v>119</v>
       </c>
-      <c r="K32" s="7">
+      <c r="L32" s="7">
         <v>78</v>
       </c>
-      <c r="L32" s="7">
+      <c r="M32" s="7">
         <v>72</v>
       </c>
-      <c r="M32" s="7">
+      <c r="N32" s="7">
         <v>83</v>
       </c>
-      <c r="O32" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P32" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>8</v>
       </c>
@@ -2159,7 +2283,7 @@
         <v>2</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D33" s="4">
         <v>4</v>
@@ -2171,28 +2295,31 @@
         <v>46160</v>
       </c>
       <c r="G33" s="6">
-        <v>2</v>
-      </c>
-      <c r="H33" s="7">
+        <v>32</v>
+      </c>
+      <c r="H33" s="6">
+        <v>2</v>
+      </c>
+      <c r="I33" s="7">
         <v>24</v>
       </c>
-      <c r="I33" s="7">
-        <v>2</v>
-      </c>
       <c r="J33" s="7">
+        <v>2</v>
+      </c>
+      <c r="K33" s="7">
         <v>119</v>
       </c>
-      <c r="K33" s="7">
+      <c r="L33" s="7">
         <v>82</v>
       </c>
-      <c r="L33" s="7">
+      <c r="M33" s="7">
         <v>66</v>
       </c>
-      <c r="M33" s="7">
+      <c r="N33" s="7">
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>9</v>
       </c>
@@ -2200,7 +2327,7 @@
         <v>1</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D34" s="4">
         <v>1</v>
@@ -2212,28 +2339,31 @@
         <v>46161</v>
       </c>
       <c r="G34" s="6">
-        <v>3</v>
-      </c>
-      <c r="H34" s="7">
+        <v>33</v>
+      </c>
+      <c r="H34" s="6">
+        <v>3</v>
+      </c>
+      <c r="I34" s="7">
         <v>35</v>
       </c>
-      <c r="I34" s="7">
-        <v>4</v>
-      </c>
       <c r="J34" s="7">
+        <v>4</v>
+      </c>
+      <c r="K34" s="7">
         <v>124</v>
       </c>
-      <c r="K34" s="7">
+      <c r="L34" s="7">
         <v>84</v>
       </c>
-      <c r="L34" s="7">
+      <c r="M34" s="7">
         <v>66</v>
       </c>
-      <c r="M34" s="7">
+      <c r="N34" s="7">
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>9</v>
       </c>
@@ -2241,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D35" s="4">
         <v>2</v>
@@ -2253,28 +2383,31 @@
         <v>46162</v>
       </c>
       <c r="G35" s="6">
-        <v>4</v>
-      </c>
-      <c r="H35" s="7">
+        <v>34</v>
+      </c>
+      <c r="H35" s="6">
+        <v>4</v>
+      </c>
+      <c r="I35" s="7">
         <v>29</v>
       </c>
-      <c r="I35" s="7">
-        <v>3</v>
-      </c>
       <c r="J35" s="7">
+        <v>3</v>
+      </c>
+      <c r="K35" s="7">
         <v>121</v>
       </c>
-      <c r="K35" s="7">
+      <c r="L35" s="7">
         <v>85</v>
       </c>
-      <c r="L35" s="7">
+      <c r="M35" s="7">
         <v>66</v>
       </c>
-      <c r="M35" s="7">
+      <c r="N35" s="7">
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>9</v>
       </c>
@@ -2282,7 +2415,7 @@
         <v>2</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D36" s="4">
         <v>3</v>
@@ -2294,28 +2427,31 @@
         <v>46163</v>
       </c>
       <c r="G36" s="6">
+        <v>35</v>
+      </c>
+      <c r="H36" s="6">
         <v>5</v>
       </c>
-      <c r="H36" s="7">
+      <c r="I36" s="7">
         <v>29</v>
       </c>
-      <c r="I36" s="7">
-        <v>3</v>
-      </c>
       <c r="J36" s="7">
+        <v>3</v>
+      </c>
+      <c r="K36" s="7">
         <v>109</v>
       </c>
-      <c r="K36" s="7">
+      <c r="L36" s="7">
         <v>77</v>
       </c>
-      <c r="L36" s="7">
+      <c r="M36" s="7">
         <v>81</v>
       </c>
-      <c r="M36" s="7">
+      <c r="N36" s="7">
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>9</v>
       </c>
@@ -2323,7 +2459,7 @@
         <v>2</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D37" s="4">
         <v>4</v>
@@ -2335,28 +2471,31 @@
         <v>46164</v>
       </c>
       <c r="G37" s="6">
+        <v>36</v>
+      </c>
+      <c r="H37" s="6">
         <v>6</v>
       </c>
-      <c r="H37" s="7">
+      <c r="I37" s="7">
         <v>36</v>
       </c>
-      <c r="I37" s="7">
-        <v>4</v>
-      </c>
       <c r="J37" s="7">
+        <v>4</v>
+      </c>
+      <c r="K37" s="7">
         <v>106</v>
       </c>
-      <c r="K37" s="7">
+      <c r="L37" s="7">
         <v>70</v>
       </c>
-      <c r="L37" s="7">
+      <c r="M37" s="7">
         <v>68</v>
       </c>
-      <c r="M37" s="7">
+      <c r="N37" s="7">
         <v>87</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>10</v>
       </c>
@@ -2364,7 +2503,7 @@
         <v>1</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D38" s="4">
         <v>1</v>
@@ -2376,28 +2515,31 @@
         <v>46165</v>
       </c>
       <c r="G38" s="6">
+        <v>37</v>
+      </c>
+      <c r="H38" s="6">
         <v>7</v>
       </c>
-      <c r="H38" s="7">
+      <c r="I38" s="7">
         <v>37</v>
       </c>
-      <c r="I38" s="7">
-        <v>4</v>
-      </c>
       <c r="J38" s="7">
+        <v>4</v>
+      </c>
+      <c r="K38" s="7">
         <v>114</v>
       </c>
-      <c r="K38" s="7">
+      <c r="L38" s="7">
         <v>80</v>
       </c>
-      <c r="L38" s="7">
+      <c r="M38" s="7">
         <v>73</v>
       </c>
-      <c r="M38" s="7">
+      <c r="N38" s="7">
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>10</v>
       </c>
@@ -2405,7 +2547,7 @@
         <v>1</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D39" s="4">
         <v>2</v>
@@ -2417,31 +2559,34 @@
         <v>46166</v>
       </c>
       <c r="G39" s="6">
+        <v>38</v>
+      </c>
+      <c r="H39" s="6">
         <v>8</v>
       </c>
-      <c r="H39" s="7">
+      <c r="I39" s="7">
         <v>26</v>
       </c>
-      <c r="I39" s="7">
-        <v>3</v>
-      </c>
       <c r="J39" s="7">
+        <v>3</v>
+      </c>
+      <c r="K39" s="7">
         <v>119</v>
       </c>
-      <c r="K39" s="7">
+      <c r="L39" s="7">
         <v>86</v>
       </c>
-      <c r="L39" s="7">
+      <c r="M39" s="7">
         <v>85</v>
       </c>
-      <c r="M39" s="7">
+      <c r="N39" s="7">
         <v>80</v>
       </c>
-      <c r="O39" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P39" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>10</v>
       </c>
@@ -2449,7 +2594,7 @@
         <v>2</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D40" s="4">
         <v>3</v>
@@ -2461,31 +2606,34 @@
         <v>46167</v>
       </c>
       <c r="G40" s="6">
-        <v>2</v>
-      </c>
-      <c r="H40" s="7">
+        <v>39</v>
+      </c>
+      <c r="H40" s="6">
+        <v>2</v>
+      </c>
+      <c r="I40" s="7">
         <v>34</v>
       </c>
-      <c r="I40" s="7">
-        <v>3</v>
-      </c>
       <c r="J40" s="7">
+        <v>3</v>
+      </c>
+      <c r="K40" s="7">
         <v>139</v>
       </c>
-      <c r="K40" s="7">
+      <c r="L40" s="7">
         <v>91</v>
       </c>
-      <c r="L40" s="7">
+      <c r="M40" s="7">
         <v>73</v>
       </c>
-      <c r="M40" s="7">
+      <c r="N40" s="7">
         <v>96</v>
       </c>
-      <c r="O40" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P40" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>10</v>
       </c>
@@ -2493,7 +2641,7 @@
         <v>2</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D41" s="4">
         <v>4</v>
@@ -2505,31 +2653,34 @@
         <v>46168</v>
       </c>
       <c r="G41" s="6">
-        <v>3</v>
-      </c>
-      <c r="H41" s="7">
+        <v>40</v>
+      </c>
+      <c r="H41" s="6">
+        <v>3</v>
+      </c>
+      <c r="I41" s="7">
         <v>48</v>
       </c>
-      <c r="I41" s="7">
+      <c r="J41" s="7">
         <v>5</v>
       </c>
-      <c r="J41" s="7">
+      <c r="K41" s="7">
         <v>110</v>
       </c>
-      <c r="K41" s="7">
+      <c r="L41" s="7">
         <v>74</v>
       </c>
-      <c r="L41" s="7">
+      <c r="M41" s="7">
         <v>73</v>
       </c>
-      <c r="M41" s="7">
+      <c r="N41" s="7">
         <v>96</v>
       </c>
-      <c r="O41" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P41" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>11</v>
       </c>
@@ -2537,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D42" s="4">
         <v>1</v>
@@ -2549,31 +2700,34 @@
         <v>46169</v>
       </c>
       <c r="G42" s="6">
-        <v>4</v>
-      </c>
-      <c r="H42" s="7">
+        <v>41</v>
+      </c>
+      <c r="H42" s="6">
+        <v>4</v>
+      </c>
+      <c r="I42" s="7">
         <v>44</v>
       </c>
-      <c r="I42" s="7">
-        <v>4</v>
-      </c>
       <c r="J42" s="7">
+        <v>4</v>
+      </c>
+      <c r="K42" s="7">
         <v>114</v>
       </c>
-      <c r="K42" s="7">
+      <c r="L42" s="7">
         <v>76</v>
       </c>
-      <c r="L42" s="7">
+      <c r="M42" s="7">
         <v>68</v>
       </c>
-      <c r="M42" s="7">
+      <c r="N42" s="7">
         <v>83</v>
       </c>
-      <c r="O42" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P42" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>11</v>
       </c>
@@ -2581,7 +2735,7 @@
         <v>1</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D43" s="4">
         <v>2</v>
@@ -2593,28 +2747,31 @@
         <v>46170</v>
       </c>
       <c r="G43" s="6">
+        <v>42</v>
+      </c>
+      <c r="H43" s="6">
         <v>5</v>
       </c>
-      <c r="H43" s="7">
+      <c r="I43" s="7">
         <v>29</v>
       </c>
-      <c r="I43" s="7">
-        <v>3</v>
-      </c>
       <c r="J43" s="7">
+        <v>3</v>
+      </c>
+      <c r="K43" s="7">
         <v>105</v>
       </c>
-      <c r="K43" s="7">
+      <c r="L43" s="7">
         <v>77</v>
       </c>
-      <c r="L43" s="7">
+      <c r="M43" s="7">
         <v>68</v>
       </c>
-      <c r="M43" s="7">
+      <c r="N43" s="7">
         <v>76</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>11</v>
       </c>
@@ -2622,7 +2779,7 @@
         <v>2</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D44" s="4">
         <v>3</v>
@@ -2634,28 +2791,31 @@
         <v>46171</v>
       </c>
       <c r="G44" s="6">
+        <v>43</v>
+      </c>
+      <c r="H44" s="6">
         <v>6</v>
       </c>
-      <c r="H44" s="7">
+      <c r="I44" s="7">
         <v>29</v>
       </c>
-      <c r="I44" s="7">
-        <v>3</v>
-      </c>
       <c r="J44" s="7">
+        <v>3</v>
+      </c>
+      <c r="K44" s="7">
         <v>120</v>
       </c>
-      <c r="K44" s="7">
+      <c r="L44" s="7">
         <v>84</v>
       </c>
-      <c r="L44" s="7">
+      <c r="M44" s="7">
         <v>64</v>
       </c>
-      <c r="M44" s="7">
+      <c r="N44" s="7">
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>11</v>
       </c>
@@ -2663,7 +2823,7 @@
         <v>2</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D45" s="4">
         <v>4</v>
@@ -2675,28 +2835,31 @@
         <v>46172</v>
       </c>
       <c r="G45" s="6">
+        <v>44</v>
+      </c>
+      <c r="H45" s="6">
         <v>7</v>
       </c>
-      <c r="H45" s="7">
+      <c r="I45" s="7">
         <v>29</v>
       </c>
-      <c r="I45" s="7">
-        <v>3</v>
-      </c>
       <c r="J45" s="7">
+        <v>3</v>
+      </c>
+      <c r="K45" s="7">
         <v>116</v>
       </c>
-      <c r="K45" s="7">
+      <c r="L45" s="7">
         <v>80</v>
       </c>
-      <c r="L45" s="7">
+      <c r="M45" s="7">
         <v>70</v>
       </c>
-      <c r="M45" s="7">
+      <c r="N45" s="7">
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>12</v>
       </c>
@@ -2704,7 +2867,7 @@
         <v>1</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D46" s="4">
         <v>1</v>
@@ -2716,31 +2879,34 @@
         <v>46173</v>
       </c>
       <c r="G46" s="6">
+        <v>45</v>
+      </c>
+      <c r="H46" s="6">
         <v>8</v>
       </c>
-      <c r="H46" s="7">
+      <c r="I46" s="7">
         <v>21</v>
       </c>
-      <c r="I46" s="7">
-        <v>2</v>
-      </c>
       <c r="J46" s="7">
+        <v>2</v>
+      </c>
+      <c r="K46" s="7">
         <v>110</v>
       </c>
-      <c r="K46" s="7">
+      <c r="L46" s="7">
         <v>76</v>
       </c>
-      <c r="L46" s="7">
+      <c r="M46" s="7">
         <v>72</v>
       </c>
-      <c r="M46" s="7">
+      <c r="N46" s="7">
         <v>92</v>
       </c>
-      <c r="O46" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P46" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>12</v>
       </c>
@@ -2748,7 +2914,7 @@
         <v>1</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D47" s="4">
         <v>2</v>
@@ -2760,28 +2926,31 @@
         <v>46174</v>
       </c>
       <c r="G47" s="6">
-        <v>2</v>
-      </c>
-      <c r="H47" s="7">
+        <v>46</v>
+      </c>
+      <c r="H47" s="6">
+        <v>2</v>
+      </c>
+      <c r="I47" s="7">
         <v>24</v>
       </c>
-      <c r="I47" s="7">
-        <v>2</v>
-      </c>
       <c r="J47" s="7">
+        <v>2</v>
+      </c>
+      <c r="K47" s="7">
         <v>115</v>
       </c>
-      <c r="K47" s="7">
+      <c r="L47" s="7">
         <v>76</v>
       </c>
-      <c r="L47" s="7">
+      <c r="M47" s="7">
         <v>59</v>
       </c>
-      <c r="M47" s="7">
+      <c r="N47" s="7">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
         <v>12</v>
       </c>
@@ -2789,7 +2958,7 @@
         <v>2</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D48" s="4">
         <v>3</v>
@@ -2800,33 +2969,36 @@
       <c r="F48" s="8">
         <v>46175</v>
       </c>
-      <c r="G48" s="9">
-        <v>3</v>
-      </c>
-      <c r="H48" s="4">
+      <c r="G48" s="6">
+        <v>47</v>
+      </c>
+      <c r="H48" s="9">
+        <v>3</v>
+      </c>
+      <c r="I48" s="4">
         <v>28</v>
       </c>
-      <c r="I48" s="4">
-        <v>3</v>
-      </c>
       <c r="J48" s="4">
+        <v>3</v>
+      </c>
+      <c r="K48" s="4">
         <v>102</v>
       </c>
-      <c r="K48" s="4">
+      <c r="L48" s="4">
         <v>72</v>
       </c>
-      <c r="L48" s="4">
+      <c r="M48" s="4">
         <v>63</v>
       </c>
-      <c r="M48" s="4">
+      <c r="N48" s="4">
         <v>84</v>
       </c>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O48" s="4"/>
+      <c r="P48" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
         <v>12</v>
       </c>
@@ -2834,7 +3006,7 @@
         <v>2</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D49" s="4">
         <v>4</v>
@@ -2845,29 +3017,32 @@
       <c r="F49" s="8">
         <v>46176</v>
       </c>
-      <c r="G49" s="9">
-        <v>4</v>
-      </c>
-      <c r="H49" s="7">
+      <c r="G49" s="6">
+        <v>48</v>
+      </c>
+      <c r="H49" s="9">
+        <v>4</v>
+      </c>
+      <c r="I49" s="7">
         <v>22</v>
       </c>
-      <c r="I49" s="7">
-        <v>2</v>
-      </c>
       <c r="J49" s="7">
+        <v>2</v>
+      </c>
+      <c r="K49" s="7">
         <v>112</v>
       </c>
-      <c r="K49" s="7">
+      <c r="L49" s="7">
         <v>73</v>
       </c>
-      <c r="L49" s="7">
+      <c r="M49" s="7">
         <v>60</v>
       </c>
-      <c r="M49" s="7">
+      <c r="N49" s="7">
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
         <v>13</v>
       </c>
@@ -2875,7 +3050,7 @@
         <v>1</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D50" s="4">
         <v>1</v>
@@ -2886,29 +3061,32 @@
       <c r="F50" s="8">
         <v>46177</v>
       </c>
-      <c r="G50" s="9">
+      <c r="G50" s="6">
+        <v>49</v>
+      </c>
+      <c r="H50" s="9">
         <v>5</v>
       </c>
-      <c r="H50" s="7">
+      <c r="I50" s="7">
         <v>28</v>
       </c>
-      <c r="I50" s="7">
-        <v>3</v>
-      </c>
       <c r="J50" s="7">
+        <v>3</v>
+      </c>
+      <c r="K50" s="7">
         <v>119</v>
       </c>
-      <c r="K50" s="7">
+      <c r="L50" s="7">
         <v>82</v>
       </c>
-      <c r="L50" s="7">
+      <c r="M50" s="7">
         <v>66</v>
       </c>
-      <c r="M50" s="7">
+      <c r="N50" s="7">
         <v>91</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
         <v>13</v>
       </c>
@@ -2916,7 +3094,7 @@
         <v>1</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D51" s="4">
         <v>2</v>
@@ -2927,29 +3105,32 @@
       <c r="F51" s="8">
         <v>46178</v>
       </c>
-      <c r="G51" s="9">
+      <c r="G51" s="6">
+        <v>50</v>
+      </c>
+      <c r="H51" s="9">
         <v>6</v>
       </c>
-      <c r="H51" s="7">
+      <c r="I51" s="7">
         <v>28</v>
       </c>
-      <c r="I51" s="7">
-        <v>3</v>
-      </c>
       <c r="J51" s="7">
+        <v>3</v>
+      </c>
+      <c r="K51" s="7">
         <v>124</v>
       </c>
-      <c r="K51" s="7">
+      <c r="L51" s="7">
         <v>70</v>
       </c>
-      <c r="L51" s="7">
+      <c r="M51" s="7">
         <v>59</v>
       </c>
-      <c r="M51" s="7">
+      <c r="N51" s="7">
         <v>80</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
         <v>13</v>
       </c>
@@ -2957,7 +3138,7 @@
         <v>2</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D52" s="4">
         <v>3</v>
@@ -2968,29 +3149,32 @@
       <c r="F52" s="8">
         <v>46179</v>
       </c>
-      <c r="G52" s="9">
+      <c r="G52" s="6">
+        <v>51</v>
+      </c>
+      <c r="H52" s="9">
         <v>7</v>
       </c>
-      <c r="H52" s="7">
+      <c r="I52" s="7">
         <v>20</v>
       </c>
-      <c r="I52" s="7">
-        <v>2</v>
-      </c>
       <c r="J52" s="7">
+        <v>2</v>
+      </c>
+      <c r="K52" s="7">
         <v>100</v>
       </c>
-      <c r="K52" s="7">
+      <c r="L52" s="7">
         <v>76</v>
       </c>
-      <c r="L52" s="7">
+      <c r="M52" s="7">
         <v>69</v>
       </c>
-      <c r="M52" s="7">
+      <c r="N52" s="7">
         <v>86</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
         <v>13</v>
       </c>
@@ -2998,7 +3182,7 @@
         <v>2</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D53" s="4">
         <v>4</v>
@@ -3009,25 +3193,28 @@
       <c r="F53" s="8">
         <v>46180</v>
       </c>
-      <c r="G53" s="9">
+      <c r="G53" s="6">
+        <v>52</v>
+      </c>
+      <c r="H53" s="9">
         <v>8</v>
       </c>
-      <c r="H53" s="7">
+      <c r="I53" s="7">
         <v>18</v>
       </c>
-      <c r="I53" s="7">
-        <v>2</v>
-      </c>
       <c r="J53" s="7">
+        <v>2</v>
+      </c>
+      <c r="K53" s="7">
         <v>123</v>
       </c>
-      <c r="K53" s="7">
+      <c r="L53" s="7">
         <v>73</v>
       </c>
-      <c r="L53" s="7">
+      <c r="M53" s="7">
         <v>64</v>
       </c>
-      <c r="M53" s="7">
+      <c r="N53" s="7">
         <v>91</v>
       </c>
     </row>
